--- a/docs/Files/ODYM_Tutorial6_RemeltingYield_V1.0_EVLIB.xlsx
+++ b/docs/Files/ODYM_Tutorial6_RemeltingYield_V1.0_EVLIB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1B8A63-965C-49D8-A52E-FE884864C1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF47B67-F68B-4F7D-861D-C0EA8A0727E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,9 +329,6 @@
     <t>Lanphear</t>
   </si>
   <si>
-    <t>ODYM_Classifications_Master_EV_LIB</t>
-  </si>
-  <si>
     <t>LIB scrap</t>
   </si>
   <si>
@@ -342,6 +339,9 @@
   </si>
   <si>
     <t>LIB materials</t>
+  </si>
+  <si>
+    <t>ODYM_Classifications_EV_LIB</t>
   </si>
 </sst>
 </file>
@@ -963,7 +963,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1181,10 +1181,13 @@
         <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="D2">
+        <v>0.94</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1201,10 +1204,13 @@
         <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>106</v>
+      </c>
+      <c r="D3">
+        <v>0.94</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1221,10 +1227,13 @@
         <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>106</v>
+      </c>
+      <c r="D4">
+        <v>0.97</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1241,10 +1250,13 @@
         <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
         <v>105</v>
       </c>
-      <c r="C5" t="s">
-        <v>106</v>
+      <c r="D5">
+        <v>0.94</v>
       </c>
       <c r="E5">
         <v>1</v>
